--- a/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
+++ b/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1069,21 +1069,18 @@
         </is>
       </c>
       <c r="D6" s="84" t="n">
-        <v>320</v>
+        <v>593.08</v>
       </c>
       <c r="E6" s="84" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="F6" s="84" t="n">
         <v>25</v>
       </c>
       <c r="G6" s="84" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="16">
-        <f>SUM(D6:G6)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H6" s="16" t="inlineStr"/>
       <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Standard height — most common</t>
@@ -1107,21 +1104,18 @@
         </is>
       </c>
       <c r="D7" s="84" t="n">
-        <v>370</v>
+        <v>682.1799999999999</v>
       </c>
       <c r="E7" s="84" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F7" s="84" t="n">
         <v>25</v>
       </c>
       <c r="G7" s="84" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="16">
-        <f>SUM(D7:G7)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H7" s="16" t="inlineStr"/>
       <c r="I7" s="21" t="inlineStr">
         <is>
           <t>Height uplift band</t>
@@ -1145,21 +1139,18 @@
         </is>
       </c>
       <c r="D8" s="84" t="n">
-        <v>420</v>
+        <v>770.1799999999999</v>
       </c>
       <c r="E8" s="84" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="F8" s="84" t="n">
         <v>25</v>
       </c>
       <c r="G8" s="84" t="n">
-        <v>35</v>
-      </c>
-      <c r="H8" s="16">
-        <f>SUM(D8:G8)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H8" s="16" t="inlineStr"/>
       <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Tallest standard band</t>
@@ -1183,21 +1174,18 @@
         </is>
       </c>
       <c r="D9" s="84" t="n">
-        <v>580</v>
+        <v>993.73</v>
       </c>
       <c r="E9" s="84" t="n">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="F9" s="84" t="n">
         <v>40</v>
       </c>
       <c r="G9" s="84" t="n">
-        <v>50</v>
-      </c>
-      <c r="H9" s="16">
-        <f>SUM(D9:G9)</f>
-        <v/>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="H9" s="16" t="inlineStr"/>
       <c r="I9" s="21" t="inlineStr">
         <is>
           <t>Double leaf</t>
@@ -1221,21 +1209,18 @@
         </is>
       </c>
       <c r="D10" s="84" t="n">
-        <v>380</v>
+        <v>593.08</v>
       </c>
       <c r="E10" s="84" t="n">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="F10" s="84" t="n">
         <v>25</v>
       </c>
       <c r="G10" s="84" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="16">
-        <f>SUM(D10:G10)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H10" s="16" t="inlineStr"/>
       <c r="I10" s="17" t="inlineStr">
         <is>
           <t>FD30S = FD30 + seals</t>
@@ -1259,21 +1244,18 @@
         </is>
       </c>
       <c r="D11" s="84" t="n">
-        <v>430</v>
+        <v>682.1799999999999</v>
       </c>
       <c r="E11" s="84" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="F11" s="84" t="n">
         <v>25</v>
       </c>
       <c r="G11" s="84" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="16">
-        <f>SUM(D11:G11)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H11" s="16" t="inlineStr"/>
       <c r="I11" s="21" t="inlineStr">
         <is>
           <t>Height uplift</t>
@@ -1297,21 +1279,18 @@
         </is>
       </c>
       <c r="D12" s="84" t="n">
-        <v>480</v>
+        <v>770.1799999999999</v>
       </c>
       <c r="E12" s="84" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="F12" s="84" t="n">
         <v>25</v>
       </c>
       <c r="G12" s="84" t="n">
-        <v>35</v>
-      </c>
-      <c r="H12" s="16">
-        <f>SUM(D12:G12)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H12" s="16" t="inlineStr"/>
       <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Tallest band</t>
@@ -1335,21 +1314,18 @@
         </is>
       </c>
       <c r="D13" s="84" t="n">
-        <v>650</v>
+        <v>993.73</v>
       </c>
       <c r="E13" s="84" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="F13" s="84" t="n">
         <v>40</v>
       </c>
       <c r="G13" s="84" t="n">
-        <v>50</v>
-      </c>
-      <c r="H13" s="16">
-        <f>SUM(D13:G13)</f>
-        <v/>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="H13" s="16" t="inlineStr"/>
       <c r="I13" s="21" t="inlineStr">
         <is>
           <t>Double leaf FD30S</t>
@@ -1373,21 +1349,18 @@
         </is>
       </c>
       <c r="D14" s="84" t="n">
-        <v>480</v>
+        <v>768.65</v>
       </c>
       <c r="E14" s="84" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="F14" s="84" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="84" t="n">
-        <v>35</v>
-      </c>
-      <c r="H14" s="16">
-        <f>SUM(D14:G14)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H14" s="16" t="inlineStr"/>
       <c r="I14" s="17" t="inlineStr">
         <is>
           <t>60-min — required by fire strategy</t>
@@ -1411,21 +1384,18 @@
         </is>
       </c>
       <c r="D15" s="84" t="n">
-        <v>540</v>
+        <v>865.15</v>
       </c>
       <c r="E15" s="84" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F15" s="84" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="84" t="n">
-        <v>35</v>
-      </c>
-      <c r="H15" s="16">
-        <f>SUM(D15:G15)</f>
-        <v/>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H15" s="16" t="inlineStr"/>
       <c r="I15" s="21" t="inlineStr">
         <is>
           <t>Height uplift</t>
@@ -1449,21 +1419,18 @@
         </is>
       </c>
       <c r="D16" s="84" t="n">
-        <v>780</v>
+        <v>1229.2</v>
       </c>
       <c r="E16" s="84" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="F16" s="84" t="n">
         <v>45</v>
       </c>
       <c r="G16" s="84" t="n">
-        <v>55</v>
-      </c>
-      <c r="H16" s="16">
-        <f>SUM(D16:G16)</f>
-        <v/>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="H16" s="16" t="inlineStr"/>
       <c r="I16" s="17" t="inlineStr">
         <is>
           <t>Double leaf FD60S</t>
@@ -1487,7 +1454,7 @@
         </is>
       </c>
       <c r="D17" s="84" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E17" s="84" t="n">
         <v>0</v>
@@ -1498,10 +1465,7 @@
       <c r="G17" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="16">
-        <f>SUM(D17:G17)</f>
-        <v/>
-      </c>
+      <c r="H17" s="16" t="inlineStr"/>
       <c r="I17" s="21" t="inlineStr">
         <is>
           <t>On top of base rate</t>
@@ -1525,7 +1489,7 @@
         </is>
       </c>
       <c r="D18" s="84" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E18" s="84" t="n">
         <v>0</v>
@@ -1536,9 +1500,10 @@
       <c r="G18" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="16">
-        <f>SUM(D18:G18)</f>
-        <v/>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Alex to confirm — under investigation</t>
+        </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -1563,21 +1528,18 @@
         </is>
       </c>
       <c r="D19" s="84" t="n">
-        <v>85</v>
+        <v>139.18</v>
       </c>
       <c r="E19" s="84" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F19" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G19" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="16">
-        <f>SUM(D19:G19)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H19" s="16" t="inlineStr"/>
       <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Supply &amp; fit fire-rated glazing</t>
@@ -1601,20 +1563,21 @@
         </is>
       </c>
       <c r="D20" s="84" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="E20" s="84" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F20" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G20" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="16">
-        <f>SUM(D20:G20)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Alex to confirm price for larger FD30 panel</t>
+        </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -1654,21 +1617,18 @@
         </is>
       </c>
       <c r="D22" s="84" t="n">
-        <v>45</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E22" s="84" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F22" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G22" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="16">
-        <f>SUM(D22:G22)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H22" s="16" t="inlineStr"/>
       <c r="I22" s="17" t="inlineStr">
         <is>
           <t>Most common remedial action</t>
@@ -1692,21 +1652,18 @@
         </is>
       </c>
       <c r="D23" s="84" t="n">
-        <v>30</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E23" s="84" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F23" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G23" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="16">
-        <f>SUM(D23:G23)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H23" s="16" t="inlineStr"/>
       <c r="I23" s="21" t="inlineStr">
         <is>
           <t>Lower spec</t>
@@ -1730,21 +1687,18 @@
         </is>
       </c>
       <c r="D24" s="84" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="E24" s="84" t="n">
-        <v>70</v>
+        <v>37.5</v>
       </c>
       <c r="F24" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G24" s="84" t="n">
-        <v>10</v>
-      </c>
-      <c r="H24" s="16">
-        <f>SUM(D24:G24)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H24" s="16" t="inlineStr"/>
       <c r="I24" s="17" t="inlineStr">
         <is>
           <t>Standard closer replacement</t>
@@ -1768,21 +1722,18 @@
         </is>
       </c>
       <c r="D25" s="84" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E25" s="84" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F25" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G25" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="16">
-        <f>SUM(D25:G25)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H25" s="16" t="inlineStr"/>
       <c r="I25" s="21" t="inlineStr">
         <is>
           <t>Check whether screws or full hinge needed</t>
@@ -1806,21 +1757,18 @@
         </is>
       </c>
       <c r="D26" s="84" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E26" s="84" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F26" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G26" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" s="16">
-        <f>SUM(D26:G26)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H26" s="16" t="inlineStr"/>
       <c r="I26" s="17" t="inlineStr">
         <is>
           <t>SSS finish unless specified</t>
@@ -1844,21 +1792,18 @@
         </is>
       </c>
       <c r="D27" s="84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E27" s="84" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F27" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G27" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H27" s="16">
-        <f>SUM(D27:G27)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H27" s="16" t="inlineStr"/>
       <c r="I27" s="21" t="inlineStr">
         <is>
           <t>Per door</t>
@@ -1882,10 +1827,10 @@
         </is>
       </c>
       <c r="D28" s="84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" s="84" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F28" s="84" t="n">
         <v>3</v>
@@ -1893,10 +1838,7 @@
       <c r="G28" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="16">
-        <f>SUM(D28:G28)</f>
-        <v/>
-      </c>
+      <c r="H28" s="16" t="inlineStr"/>
       <c r="I28" s="17" t="inlineStr">
         <is>
           <t>Per door — 2 signs per leaf</t>
@@ -1920,20 +1862,21 @@
         </is>
       </c>
       <c r="D29" s="84" t="n">
-        <v>180</v>
+        <v>325</v>
       </c>
       <c r="E29" s="84" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F29" s="84" t="n">
         <v>10</v>
       </c>
       <c r="G29" s="84" t="n">
-        <v>15</v>
-      </c>
-      <c r="H29" s="16">
-        <f>SUM(D29:G29)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Alex cannot price access control items — quote separately per job</t>
+        </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
@@ -1958,20 +1901,21 @@
         </is>
       </c>
       <c r="D30" s="84" t="n">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="E30" s="84" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F30" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G30" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H30" s="16">
-        <f>SUM(D30:G30)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Alex cannot price access control items — quote separately per job</t>
+        </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -1996,20 +1940,21 @@
         </is>
       </c>
       <c r="D31" s="84" t="n">
+        <v>300</v>
+      </c>
+      <c r="E31" s="84" t="n">
         <v>0</v>
-      </c>
-      <c r="E31" s="84" t="n">
-        <v>75</v>
       </c>
       <c r="F31" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G31" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="16">
-        <f>SUM(D31:G31)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Hourly rate £37.50/hr or minimum 1 day carpenter £300 cost — Matt to confirm per-door rate</t>
+        </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
@@ -2034,21 +1979,18 @@
         </is>
       </c>
       <c r="D32" s="84" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E32" s="84" t="n">
-        <v>85</v>
+        <v>37.5</v>
       </c>
       <c r="F32" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G32" s="84" t="n">
-        <v>10</v>
-      </c>
-      <c r="H32" s="16">
-        <f>SUM(D32:G32)</f>
-        <v/>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H32" s="16" t="inlineStr"/>
       <c r="I32" s="25" t="inlineStr">
         <is>
           <t>Covers ART 01 in EAS/FireDNA system. Common fault — appears on ~20% of doors surveyed.</t>
@@ -2072,20 +2014,21 @@
         </is>
       </c>
       <c r="D33" s="84" t="n">
-        <v>35</v>
+        <v>500</v>
       </c>
       <c r="E33" s="84" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F33" s="84" t="n">
         <v>5</v>
       </c>
       <c r="G33" s="84" t="n">
-        <v>10</v>
-      </c>
-      <c r="H33" s="16">
-        <f>SUM(D33:G33)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Hourly rate £62.50/hr or minimum 1 day magic man £500 cost — Matt to confirm per-door rate</t>
+        </is>
       </c>
       <c r="I33" s="25" t="inlineStr">
         <is>
@@ -2125,20 +2068,21 @@
         </is>
       </c>
       <c r="D35" s="84" t="n">
+        <v>170</v>
+      </c>
+      <c r="E35" s="84" t="n">
         <v>0</v>
-      </c>
-      <c r="E35" s="84" t="n">
-        <v>120</v>
       </c>
       <c r="F35" s="84" t="n">
         <v>20</v>
       </c>
       <c r="G35" s="84" t="n">
-        <v>30</v>
-      </c>
-      <c r="H35" s="16">
-        <f>SUM(D35:G35)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Alex to confirm call-out rate</t>
+        </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
@@ -2163,20 +2107,21 @@
         </is>
       </c>
       <c r="D36" s="84" t="n">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="E36" s="84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F36" s="84" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="84" t="n">
-        <v>10</v>
-      </c>
-      <c r="H36" s="16">
-        <f>SUM(D36:G36)</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Alex: £300 minimum per visit — not per door. Matt to confirm how to allocate across jobs</t>
+        </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
@@ -2201,10 +2146,10 @@
         </is>
       </c>
       <c r="D37" s="84" t="n">
+        <v>40</v>
+      </c>
+      <c r="E37" s="84" t="n">
         <v>0</v>
-      </c>
-      <c r="E37" s="84" t="n">
-        <v>35</v>
       </c>
       <c r="F37" s="84" t="n">
         <v>5</v>
@@ -2212,9 +2157,10 @@
       <c r="G37" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="16">
-        <f>SUM(D37:G37)</f>
-        <v/>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Alex to confirm per-door certification rate</t>
+        </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
@@ -2277,7 +2223,7 @@
         </is>
       </c>
       <c r="D39" s="84" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E39" s="84" t="n">
         <v>0</v>
@@ -2288,9 +2234,10 @@
       <c r="G39" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="16">
-        <f>SUM(D39:G39)</f>
-        <v/>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>⚠️ MOCK RATE: Job by job basis — Alex cannot provide standard rate</t>
+        </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -2298,6 +2245,16 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>

--- a/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
+++ b/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
@@ -1075,7 +1075,7 @@
         <v>250</v>
       </c>
       <c r="F6" s="84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G6" s="84" t="n">
         <v>40</v>
@@ -1110,7 +1110,7 @@
         <v>250</v>
       </c>
       <c r="F7" s="84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G7" s="84" t="n">
         <v>40</v>
@@ -1145,7 +1145,7 @@
         <v>250</v>
       </c>
       <c r="F8" s="84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G8" s="84" t="n">
         <v>40</v>
@@ -1180,7 +1180,7 @@
         <v>350</v>
       </c>
       <c r="F9" s="84" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G9" s="84" t="n">
         <v>80</v>
@@ -1215,7 +1215,7 @@
         <v>250</v>
       </c>
       <c r="F10" s="84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G10" s="84" t="n">
         <v>40</v>
@@ -1250,7 +1250,7 @@
         <v>250</v>
       </c>
       <c r="F11" s="84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G11" s="84" t="n">
         <v>40</v>
@@ -1285,7 +1285,7 @@
         <v>250</v>
       </c>
       <c r="F12" s="84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G12" s="84" t="n">
         <v>40</v>
@@ -1320,7 +1320,7 @@
         <v>350</v>
       </c>
       <c r="F13" s="84" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G13" s="84" t="n">
         <v>80</v>
@@ -1355,7 +1355,7 @@
         <v>250</v>
       </c>
       <c r="F14" s="84" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G14" s="84" t="n">
         <v>40</v>
@@ -1390,7 +1390,7 @@
         <v>250</v>
       </c>
       <c r="F15" s="84" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G15" s="84" t="n">
         <v>40</v>
@@ -1425,7 +1425,7 @@
         <v>350</v>
       </c>
       <c r="F16" s="84" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G16" s="84" t="n">
         <v>80</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="H18" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Alex to confirm — under investigation</t>
+          <t>⚠️ MOCK: Alex to confirm — under investigation</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" s="84" t="n">
         <v>0</v>
@@ -1569,14 +1569,14 @@
         <v>0</v>
       </c>
       <c r="F20" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20" s="84" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Alex to confirm price for larger FD30 panel</t>
+          <t>⚠️ MOCK: Alex to confirm price for larger FD30 panel</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
@@ -1623,7 +1623,7 @@
         <v>75</v>
       </c>
       <c r="F22" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G22" s="84" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
         <v>75</v>
       </c>
       <c r="F23" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G23" s="84" t="n">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>37.5</v>
       </c>
       <c r="F24" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="84" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
         <v>75</v>
       </c>
       <c r="F25" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G25" s="84" t="n">
         <v>0</v>
@@ -1763,7 +1763,7 @@
         <v>75</v>
       </c>
       <c r="F26" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26" s="84" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>75</v>
       </c>
       <c r="F27" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G27" s="84" t="n">
         <v>0</v>
@@ -1833,7 +1833,7 @@
         <v>37.5</v>
       </c>
       <c r="F28" s="84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" s="84" t="n">
         <v>0</v>
@@ -1868,14 +1868,14 @@
         <v>0</v>
       </c>
       <c r="F29" s="84" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G29" s="84" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Alex cannot price access control items — quote separately per job</t>
+          <t>⚠️ MOCK: Alex cannot price access control items — quote separately per job</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -1907,14 +1907,14 @@
         <v>0</v>
       </c>
       <c r="F30" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G30" s="84" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Alex cannot price access control items — quote separately per job</t>
+          <t>⚠️ MOCK: Alex cannot price access control items — quote separately per job</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
@@ -1946,14 +1946,14 @@
         <v>0</v>
       </c>
       <c r="F31" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G31" s="84" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Hourly rate £37.50/hr or minimum 1 day carpenter £300 cost — Matt to confirm per-door rate</t>
+          <t>⚠️ MOCK: Hourly rate £37.50/hr or minimum 1 day carpenter £300 cost — Matt to confirm per-door rate</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -1985,7 +1985,7 @@
         <v>37.5</v>
       </c>
       <c r="F32" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G32" s="84" t="n">
         <v>0</v>
@@ -2020,14 +2020,14 @@
         <v>0</v>
       </c>
       <c r="F33" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G33" s="84" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Hourly rate £62.50/hr or minimum 1 day magic man £500 cost — Matt to confirm per-door rate</t>
+          <t>⚠️ MOCK: Hourly rate £62.50/hr or minimum 1 day magic man £500 cost — Matt to confirm per-door rate</t>
         </is>
       </c>
       <c r="I33" s="25" t="inlineStr">
@@ -2074,14 +2074,14 @@
         <v>0</v>
       </c>
       <c r="F35" s="84" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G35" s="84" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Alex to confirm call-out rate</t>
+          <t>⚠️ MOCK: Alex to confirm call-out rate</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H36" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Alex: £300 minimum per visit — not per door. Matt to confirm how to allocate across jobs</t>
+          <t>⚠️ MOCK: Alex: £300 minimum per visit — not per door. Matt to confirm how to allocate across jobs</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
@@ -2152,14 +2152,14 @@
         <v>0</v>
       </c>
       <c r="F37" s="84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G37" s="84" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Alex to confirm per-door certification rate</t>
+          <t>⚠️ MOCK: Alex to confirm per-door certification rate</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>⚠️ MOCK RATE: Job by job basis — Alex cannot provide standard rate</t>
+          <t>⚠️ MOCK: Job by job basis — Alex cannot provide standard rate</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">

--- a/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
+++ b/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
@@ -949,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1086,6 +1086,7 @@
           <t>Standard height — most common</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
@@ -1121,6 +1122,7 @@
           <t>Height uplift band</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -1156,6 +1158,7 @@
           <t>Tallest standard band</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
@@ -1191,6 +1194,7 @@
           <t>Double leaf</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -1226,6 +1230,7 @@
           <t>FD30S = FD30 + seals</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -1261,6 +1266,7 @@
           <t>Height uplift</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -1296,6 +1302,7 @@
           <t>Tallest band</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -1331,6 +1338,7 @@
           <t>Double leaf FD30S</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -1366,6 +1374,7 @@
           <t>60-min — required by fire strategy</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
@@ -1401,6 +1410,7 @@
           <t>Height uplift</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -1436,6 +1446,7 @@
           <t>Double leaf FD60S</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -1471,6 +1482,7 @@
           <t>On top of base rate</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1500,14 +1512,15 @@
       <c r="G18" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H18" s="16" t="n"/>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>On top of base rate</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Alex to confirm — under investigation</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>On top of base rate</t>
         </is>
       </c>
     </row>
@@ -1545,6 +1558,7 @@
           <t>Supply &amp; fit fire-rated glazing</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -1574,14 +1588,15 @@
       <c r="G20" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>Larger vision panel</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Alex to confirm price for larger FD30 panel</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>Larger vision panel</t>
         </is>
       </c>
     </row>
@@ -1634,6 +1649,7 @@
           <t>Most common remedial action</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
@@ -1669,6 +1685,7 @@
           <t>Lower spec</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -1704,6 +1721,7 @@
           <t>Standard closer replacement</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
@@ -1739,6 +1757,7 @@
           <t>Check whether screws or full hinge needed</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -1774,6 +1793,7 @@
           <t>SSS finish unless specified</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
@@ -1809,6 +1829,7 @@
           <t>Per door</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -1844,6 +1865,7 @@
           <t>Per door — 2 signs per leaf</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
@@ -1873,14 +1895,15 @@
       <c r="G29" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H29" s="16" t="n"/>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>Requires electrical connection</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Alex cannot price access control items — quote separately per job</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>Requires electrical connection</t>
         </is>
       </c>
     </row>
@@ -1912,14 +1935,15 @@
       <c r="G30" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H30" s="16" t="n"/>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>Per door</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Alex cannot price access control items — quote separately per job</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>Per door</t>
         </is>
       </c>
     </row>
@@ -1951,14 +1975,15 @@
       <c r="G31" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H31" s="16" t="n"/>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>Labour only</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Hourly rate £37.50/hr or minimum 1 day carpenter £300 cost — Matt to confirm per-door rate</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>Labour only</t>
         </is>
       </c>
     </row>
@@ -1996,6 +2021,7 @@
           <t>Covers ART 01 in EAS/FireDNA system. Common fault — appears on ~20% of doors surveyed.</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
@@ -2025,14 +2051,15 @@
       <c r="G33" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H33" s="16" t="n"/>
+      <c r="I33" s="25" t="inlineStr">
+        <is>
+          <t>Covers ART 02 in EAS/FireDNA system. Appears frequently on tenant doors. Per hole/void.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Hourly rate £62.50/hr or minimum 1 day magic man £500 cost — Matt to confirm per-door rate</t>
-        </is>
-      </c>
-      <c r="I33" s="25" t="inlineStr">
-        <is>
-          <t>Covers ART 02 in EAS/FireDNA system. Appears frequently on tenant doors. Per hole/void.</t>
         </is>
       </c>
     </row>
@@ -2079,14 +2106,15 @@
       <c r="G35" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H35" s="16" t="n"/>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>Travel, van, tools, PPE</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Alex to confirm call-out rate</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>Travel, van, tools, PPE</t>
         </is>
       </c>
     </row>
@@ -2118,14 +2146,15 @@
       <c r="G36" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H36" s="16" t="n"/>
+      <c r="I36" s="17" t="inlineStr">
+        <is>
+          <t>Removed doors, packaging, debris</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Alex: £300 minimum per visit — not per door. Matt to confirm how to allocate across jobs</t>
-        </is>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>Removed doors, packaging, debris</t>
         </is>
       </c>
     </row>
@@ -2157,14 +2186,15 @@
       <c r="G37" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H37" s="16" t="n"/>
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>Photo record, cert, handover pack</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Alex to confirm per-door certification rate</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>Photo record, cert, handover pack</t>
         </is>
       </c>
     </row>
@@ -2234,14 +2264,15 @@
       <c r="G39" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="H39" s="16" t="n"/>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>Where standard access not possible</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>⚠️ MOCK: Job by job basis — Alex cannot provide standard rate</t>
-        </is>
-      </c>
-      <c r="I39" s="21" t="inlineStr">
-        <is>
-          <t>Where standard access not possible</t>
         </is>
       </c>
     </row>

--- a/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
+++ b/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
@@ -1075,10 +1075,11 @@
         <v>250</v>
       </c>
       <c r="F6" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G6" s="84">
+        <f>SUM(D6:F6)</f>
+        <v/>
       </c>
       <c r="H6" s="16" t="inlineStr"/>
       <c r="I6" s="17" t="inlineStr">
@@ -1086,7 +1087,6 @@
           <t>Standard height — most common</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
@@ -1111,10 +1111,11 @@
         <v>250</v>
       </c>
       <c r="F7" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G7" s="84">
+        <f>SUM(D7:F7)</f>
+        <v/>
       </c>
       <c r="H7" s="16" t="inlineStr"/>
       <c r="I7" s="21" t="inlineStr">
@@ -1122,7 +1123,6 @@
           <t>Height uplift band</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -1147,10 +1147,11 @@
         <v>250</v>
       </c>
       <c r="F8" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G8" s="84">
+        <f>SUM(D8:F8)</f>
+        <v/>
       </c>
       <c r="H8" s="16" t="inlineStr"/>
       <c r="I8" s="17" t="inlineStr">
@@ -1158,7 +1159,6 @@
           <t>Tallest standard band</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
@@ -1183,10 +1183,11 @@
         <v>350</v>
       </c>
       <c r="F9" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="84" t="n">
         <v>80</v>
+      </c>
+      <c r="G9" s="84">
+        <f>SUM(D9:F9)</f>
+        <v/>
       </c>
       <c r="H9" s="16" t="inlineStr"/>
       <c r="I9" s="21" t="inlineStr">
@@ -1194,7 +1195,6 @@
           <t>Double leaf</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -1219,10 +1219,11 @@
         <v>250</v>
       </c>
       <c r="F10" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G10" s="84">
+        <f>SUM(D10:F10)</f>
+        <v/>
       </c>
       <c r="H10" s="16" t="inlineStr"/>
       <c r="I10" s="17" t="inlineStr">
@@ -1230,7 +1231,6 @@
           <t>FD30S = FD30 + seals</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -1255,10 +1255,11 @@
         <v>250</v>
       </c>
       <c r="F11" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G11" s="84">
+        <f>SUM(D11:F11)</f>
+        <v/>
       </c>
       <c r="H11" s="16" t="inlineStr"/>
       <c r="I11" s="21" t="inlineStr">
@@ -1266,7 +1267,6 @@
           <t>Height uplift</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -1291,10 +1291,11 @@
         <v>250</v>
       </c>
       <c r="F12" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G12" s="84">
+        <f>SUM(D12:F12)</f>
+        <v/>
       </c>
       <c r="H12" s="16" t="inlineStr"/>
       <c r="I12" s="17" t="inlineStr">
@@ -1302,7 +1303,6 @@
           <t>Tallest band</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -1327,10 +1327,11 @@
         <v>350</v>
       </c>
       <c r="F13" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="84" t="n">
         <v>80</v>
+      </c>
+      <c r="G13" s="84">
+        <f>SUM(D13:F13)</f>
+        <v/>
       </c>
       <c r="H13" s="16" t="inlineStr"/>
       <c r="I13" s="21" t="inlineStr">
@@ -1338,7 +1339,6 @@
           <t>Double leaf FD30S</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -1363,10 +1363,11 @@
         <v>250</v>
       </c>
       <c r="F14" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G14" s="84">
+        <f>SUM(D14:F14)</f>
+        <v/>
       </c>
       <c r="H14" s="16" t="inlineStr"/>
       <c r="I14" s="17" t="inlineStr">
@@ -1374,7 +1375,6 @@
           <t>60-min — required by fire strategy</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
@@ -1399,10 +1399,11 @@
         <v>250</v>
       </c>
       <c r="F15" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="84" t="n">
         <v>40</v>
+      </c>
+      <c r="G15" s="84">
+        <f>SUM(D15:F15)</f>
+        <v/>
       </c>
       <c r="H15" s="16" t="inlineStr"/>
       <c r="I15" s="21" t="inlineStr">
@@ -1410,7 +1411,6 @@
           <t>Height uplift</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -1435,10 +1435,11 @@
         <v>350</v>
       </c>
       <c r="F16" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="84" t="n">
         <v>80</v>
+      </c>
+      <c r="G16" s="84">
+        <f>SUM(D16:F16)</f>
+        <v/>
       </c>
       <c r="H16" s="16" t="inlineStr"/>
       <c r="I16" s="17" t="inlineStr">
@@ -1446,7 +1447,6 @@
           <t>Double leaf FD60S</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -1473,8 +1473,9 @@
       <c r="F17" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="84" t="n">
-        <v>0</v>
+      <c r="G17" s="84">
+        <f>SUM(D17:F17)</f>
+        <v/>
       </c>
       <c r="H17" s="16" t="inlineStr"/>
       <c r="I17" s="21" t="inlineStr">
@@ -1482,7 +1483,6 @@
           <t>On top of base rate</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1509,8 +1509,9 @@
       <c r="F18" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="84" t="n">
-        <v>0</v>
+      <c r="G18" s="84">
+        <f>SUM(D18:F18)</f>
+        <v/>
       </c>
       <c r="H18" s="16" t="n"/>
       <c r="I18" s="17" t="inlineStr">
@@ -1549,8 +1550,9 @@
       <c r="F19" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="84" t="n">
-        <v>0</v>
+      <c r="G19" s="84">
+        <f>SUM(D19:F19)</f>
+        <v/>
       </c>
       <c r="H19" s="16" t="inlineStr"/>
       <c r="I19" s="21" t="inlineStr">
@@ -1558,7 +1560,6 @@
           <t>Supply &amp; fit fire-rated glazing</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -1585,8 +1586,9 @@
       <c r="F20" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="84" t="n">
-        <v>0</v>
+      <c r="G20" s="84">
+        <f>SUM(D20:F20)</f>
+        <v/>
       </c>
       <c r="H20" s="16" t="n"/>
       <c r="I20" s="17" t="inlineStr">
@@ -1640,8 +1642,9 @@
       <c r="F22" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="84" t="n">
-        <v>0</v>
+      <c r="G22" s="84">
+        <f>SUM(D22:F22)</f>
+        <v/>
       </c>
       <c r="H22" s="16" t="inlineStr"/>
       <c r="I22" s="17" t="inlineStr">
@@ -1649,7 +1652,6 @@
           <t>Most common remedial action</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
@@ -1676,8 +1678,9 @@
       <c r="F23" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="84" t="n">
-        <v>0</v>
+      <c r="G23" s="84">
+        <f>SUM(D23:F23)</f>
+        <v/>
       </c>
       <c r="H23" s="16" t="inlineStr"/>
       <c r="I23" s="21" t="inlineStr">
@@ -1685,7 +1688,6 @@
           <t>Lower spec</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -1712,8 +1714,9 @@
       <c r="F24" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="84" t="n">
-        <v>0</v>
+      <c r="G24" s="84">
+        <f>SUM(D24:F24)</f>
+        <v/>
       </c>
       <c r="H24" s="16" t="inlineStr"/>
       <c r="I24" s="17" t="inlineStr">
@@ -1721,7 +1724,6 @@
           <t>Standard closer replacement</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
@@ -1748,8 +1750,9 @@
       <c r="F25" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="84" t="n">
-        <v>0</v>
+      <c r="G25" s="84">
+        <f>SUM(D25:F25)</f>
+        <v/>
       </c>
       <c r="H25" s="16" t="inlineStr"/>
       <c r="I25" s="21" t="inlineStr">
@@ -1757,7 +1760,6 @@
           <t>Check whether screws or full hinge needed</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -1784,8 +1786,9 @@
       <c r="F26" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="84" t="n">
-        <v>0</v>
+      <c r="G26" s="84">
+        <f>SUM(D26:F26)</f>
+        <v/>
       </c>
       <c r="H26" s="16" t="inlineStr"/>
       <c r="I26" s="17" t="inlineStr">
@@ -1793,7 +1796,6 @@
           <t>SSS finish unless specified</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
@@ -1820,8 +1822,9 @@
       <c r="F27" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="84" t="n">
-        <v>0</v>
+      <c r="G27" s="84">
+        <f>SUM(D27:F27)</f>
+        <v/>
       </c>
       <c r="H27" s="16" t="inlineStr"/>
       <c r="I27" s="21" t="inlineStr">
@@ -1829,7 +1832,6 @@
           <t>Per door</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -1856,8 +1858,9 @@
       <c r="F28" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="84" t="n">
-        <v>0</v>
+      <c r="G28" s="84">
+        <f>SUM(D28:F28)</f>
+        <v/>
       </c>
       <c r="H28" s="16" t="inlineStr"/>
       <c r="I28" s="17" t="inlineStr">
@@ -1865,7 +1868,6 @@
           <t>Per door — 2 signs per leaf</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
@@ -1892,8 +1894,9 @@
       <c r="F29" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="84" t="n">
-        <v>0</v>
+      <c r="G29" s="84">
+        <f>SUM(D29:F29)</f>
+        <v/>
       </c>
       <c r="H29" s="16" t="n"/>
       <c r="I29" s="21" t="inlineStr">
@@ -1932,8 +1935,9 @@
       <c r="F30" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="84" t="n">
-        <v>0</v>
+      <c r="G30" s="84">
+        <f>SUM(D30:F30)</f>
+        <v/>
       </c>
       <c r="H30" s="16" t="n"/>
       <c r="I30" s="17" t="inlineStr">
@@ -1972,8 +1976,9 @@
       <c r="F31" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="84" t="n">
-        <v>0</v>
+      <c r="G31" s="84">
+        <f>SUM(D31:F31)</f>
+        <v/>
       </c>
       <c r="H31" s="16" t="n"/>
       <c r="I31" s="21" t="inlineStr">
@@ -2012,8 +2017,9 @@
       <c r="F32" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="84" t="n">
-        <v>0</v>
+      <c r="G32" s="84">
+        <f>SUM(D32:F32)</f>
+        <v/>
       </c>
       <c r="H32" s="16" t="inlineStr"/>
       <c r="I32" s="25" t="inlineStr">
@@ -2021,7 +2027,6 @@
           <t>Covers ART 01 in EAS/FireDNA system. Common fault — appears on ~20% of doors surveyed.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
@@ -2048,8 +2053,9 @@
       <c r="F33" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="84" t="n">
-        <v>0</v>
+      <c r="G33" s="84">
+        <f>SUM(D33:F33)</f>
+        <v/>
       </c>
       <c r="H33" s="16" t="n"/>
       <c r="I33" s="25" t="inlineStr">
@@ -2103,8 +2109,9 @@
       <c r="F35" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="84" t="n">
-        <v>0</v>
+      <c r="G35" s="84">
+        <f>SUM(D35:F35)</f>
+        <v/>
       </c>
       <c r="H35" s="16" t="n"/>
       <c r="I35" s="21" t="inlineStr">
@@ -2143,8 +2150,9 @@
       <c r="F36" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="84" t="n">
-        <v>0</v>
+      <c r="G36" s="84">
+        <f>SUM(D36:F36)</f>
+        <v/>
       </c>
       <c r="H36" s="16" t="n"/>
       <c r="I36" s="17" t="inlineStr">
@@ -2183,8 +2191,9 @@
       <c r="F37" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="84" t="n">
-        <v>0</v>
+      <c r="G37" s="84">
+        <f>SUM(D37:F37)</f>
+        <v/>
       </c>
       <c r="H37" s="16" t="n"/>
       <c r="I37" s="21" t="inlineStr">
@@ -2223,8 +2232,9 @@
       <c r="F38" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="84" t="n">
-        <v>0</v>
+      <c r="G38" s="84">
+        <f>SUM(D38:F38)</f>
+        <v/>
       </c>
       <c r="H38" s="16">
         <f>SUM(D38:G38)</f>
@@ -2261,8 +2271,9 @@
       <c r="F39" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="84" t="n">
-        <v>0</v>
+      <c r="G39" s="84">
+        <f>SUM(D39:F39)</f>
+        <v/>
       </c>
       <c r="H39" s="16" t="n"/>
       <c r="I39" s="21" t="inlineStr">

--- a/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
+++ b/backend/reference_files/WestPark_FireDoor_CostSheet_v3_AlphaSights.xlsx
@@ -1077,9 +1077,8 @@
       <c r="F6" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="84">
-        <f>SUM(D6:F6)</f>
-        <v/>
+      <c r="G6" s="84" t="n">
+        <v>883.08</v>
       </c>
       <c r="H6" s="16" t="inlineStr"/>
       <c r="I6" s="17" t="inlineStr">
@@ -1087,6 +1086,7 @@
           <t>Standard height — most common</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
@@ -1113,9 +1113,8 @@
       <c r="F7" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G7" s="84">
-        <f>SUM(D7:F7)</f>
-        <v/>
+      <c r="G7" s="84" t="n">
+        <v>972.1799999999999</v>
       </c>
       <c r="H7" s="16" t="inlineStr"/>
       <c r="I7" s="21" t="inlineStr">
@@ -1123,6 +1122,7 @@
           <t>Height uplift band</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -1149,9 +1149,8 @@
       <c r="F8" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G8" s="84">
-        <f>SUM(D8:F8)</f>
-        <v/>
+      <c r="G8" s="84" t="n">
+        <v>1060.18</v>
       </c>
       <c r="H8" s="16" t="inlineStr"/>
       <c r="I8" s="17" t="inlineStr">
@@ -1159,6 +1158,7 @@
           <t>Tallest standard band</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
@@ -1185,9 +1185,8 @@
       <c r="F9" s="84" t="n">
         <v>80</v>
       </c>
-      <c r="G9" s="84">
-        <f>SUM(D9:F9)</f>
-        <v/>
+      <c r="G9" s="84" t="n">
+        <v>1423.73</v>
       </c>
       <c r="H9" s="16" t="inlineStr"/>
       <c r="I9" s="21" t="inlineStr">
@@ -1195,6 +1194,7 @@
           <t>Double leaf</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -1221,9 +1221,8 @@
       <c r="F10" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="84">
-        <f>SUM(D10:F10)</f>
-        <v/>
+      <c r="G10" s="84" t="n">
+        <v>883.08</v>
       </c>
       <c r="H10" s="16" t="inlineStr"/>
       <c r="I10" s="17" t="inlineStr">
@@ -1231,6 +1230,7 @@
           <t>FD30S = FD30 + seals</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -1257,9 +1257,8 @@
       <c r="F11" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G11" s="84">
-        <f>SUM(D11:F11)</f>
-        <v/>
+      <c r="G11" s="84" t="n">
+        <v>972.1799999999999</v>
       </c>
       <c r="H11" s="16" t="inlineStr"/>
       <c r="I11" s="21" t="inlineStr">
@@ -1267,6 +1266,7 @@
           <t>Height uplift</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -1293,9 +1293,8 @@
       <c r="F12" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G12" s="84">
-        <f>SUM(D12:F12)</f>
-        <v/>
+      <c r="G12" s="84" t="n">
+        <v>1060.18</v>
       </c>
       <c r="H12" s="16" t="inlineStr"/>
       <c r="I12" s="17" t="inlineStr">
@@ -1303,6 +1302,7 @@
           <t>Tallest band</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -1329,9 +1329,8 @@
       <c r="F13" s="84" t="n">
         <v>80</v>
       </c>
-      <c r="G13" s="84">
-        <f>SUM(D13:F13)</f>
-        <v/>
+      <c r="G13" s="84" t="n">
+        <v>1423.73</v>
       </c>
       <c r="H13" s="16" t="inlineStr"/>
       <c r="I13" s="21" t="inlineStr">
@@ -1339,6 +1338,7 @@
           <t>Double leaf FD30S</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -1365,9 +1365,8 @@
       <c r="F14" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G14" s="84">
-        <f>SUM(D14:F14)</f>
-        <v/>
+      <c r="G14" s="84" t="n">
+        <v>1058.65</v>
       </c>
       <c r="H14" s="16" t="inlineStr"/>
       <c r="I14" s="17" t="inlineStr">
@@ -1375,6 +1374,7 @@
           <t>60-min — required by fire strategy</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
@@ -1401,9 +1401,8 @@
       <c r="F15" s="84" t="n">
         <v>40</v>
       </c>
-      <c r="G15" s="84">
-        <f>SUM(D15:F15)</f>
-        <v/>
+      <c r="G15" s="84" t="n">
+        <v>1155.15</v>
       </c>
       <c r="H15" s="16" t="inlineStr"/>
       <c r="I15" s="21" t="inlineStr">
@@ -1411,6 +1410,7 @@
           <t>Height uplift</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -1437,9 +1437,8 @@
       <c r="F16" s="84" t="n">
         <v>80</v>
       </c>
-      <c r="G16" s="84">
-        <f>SUM(D16:F16)</f>
-        <v/>
+      <c r="G16" s="84" t="n">
+        <v>1659.2</v>
       </c>
       <c r="H16" s="16" t="inlineStr"/>
       <c r="I16" s="17" t="inlineStr">
@@ -1447,6 +1446,7 @@
           <t>Double leaf FD60S</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -1473,9 +1473,8 @@
       <c r="F17" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="84">
-        <f>SUM(D17:F17)</f>
-        <v/>
+      <c r="G17" s="84" t="n">
+        <v>100</v>
       </c>
       <c r="H17" s="16" t="inlineStr"/>
       <c r="I17" s="21" t="inlineStr">
@@ -1483,6 +1482,7 @@
           <t>On top of base rate</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
@@ -1509,9 +1509,8 @@
       <c r="F18" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="84">
-        <f>SUM(D18:F18)</f>
-        <v/>
+      <c r="G18" s="84" t="n">
+        <v>150</v>
       </c>
       <c r="H18" s="16" t="n"/>
       <c r="I18" s="17" t="inlineStr">
@@ -1550,9 +1549,8 @@
       <c r="F19" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="84">
-        <f>SUM(D19:F19)</f>
-        <v/>
+      <c r="G19" s="84" t="n">
+        <v>139.18</v>
       </c>
       <c r="H19" s="16" t="inlineStr"/>
       <c r="I19" s="21" t="inlineStr">
@@ -1560,6 +1558,7 @@
           <t>Supply &amp; fit fire-rated glazing</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
@@ -1586,9 +1585,8 @@
       <c r="F20" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="84">
-        <f>SUM(D20:F20)</f>
-        <v/>
+      <c r="G20" s="84" t="n">
+        <v>200</v>
       </c>
       <c r="H20" s="16" t="n"/>
       <c r="I20" s="17" t="inlineStr">
@@ -1642,9 +1640,8 @@
       <c r="F22" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="84">
-        <f>SUM(D22:F22)</f>
-        <v/>
+      <c r="G22" s="84" t="n">
+        <v>142.65</v>
       </c>
       <c r="H22" s="16" t="inlineStr"/>
       <c r="I22" s="17" t="inlineStr">
@@ -1652,6 +1649,7 @@
           <t>Most common remedial action</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
@@ -1678,9 +1676,8 @@
       <c r="F23" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="84">
-        <f>SUM(D23:F23)</f>
-        <v/>
+      <c r="G23" s="84" t="n">
+        <v>142.65</v>
       </c>
       <c r="H23" s="16" t="inlineStr"/>
       <c r="I23" s="21" t="inlineStr">
@@ -1688,6 +1685,7 @@
           <t>Lower spec</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
@@ -1714,9 +1712,8 @@
       <c r="F24" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="84">
-        <f>SUM(D24:F24)</f>
-        <v/>
+      <c r="G24" s="84" t="n">
+        <v>82.5</v>
       </c>
       <c r="H24" s="16" t="inlineStr"/>
       <c r="I24" s="17" t="inlineStr">
@@ -1724,6 +1721,7 @@
           <t>Standard closer replacement</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
@@ -1750,9 +1748,8 @@
       <c r="F25" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="84">
-        <f>SUM(D25:F25)</f>
-        <v/>
+      <c r="G25" s="84" t="n">
+        <v>90</v>
       </c>
       <c r="H25" s="16" t="inlineStr"/>
       <c r="I25" s="21" t="inlineStr">
@@ -1760,6 +1757,7 @@
           <t>Check whether screws or full hinge needed</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
@@ -1786,9 +1784,8 @@
       <c r="F26" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="84">
-        <f>SUM(D26:F26)</f>
-        <v/>
+      <c r="G26" s="84" t="n">
+        <v>100</v>
       </c>
       <c r="H26" s="16" t="inlineStr"/>
       <c r="I26" s="17" t="inlineStr">
@@ -1796,6 +1793,7 @@
           <t>SSS finish unless specified</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
@@ -1822,9 +1820,8 @@
       <c r="F27" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="84">
-        <f>SUM(D27:F27)</f>
-        <v/>
+      <c r="G27" s="84" t="n">
+        <v>85</v>
       </c>
       <c r="H27" s="16" t="inlineStr"/>
       <c r="I27" s="21" t="inlineStr">
@@ -1832,6 +1829,7 @@
           <t>Per door</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
@@ -1858,9 +1856,8 @@
       <c r="F28" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="84">
-        <f>SUM(D28:F28)</f>
-        <v/>
+      <c r="G28" s="84" t="n">
+        <v>47.5</v>
       </c>
       <c r="H28" s="16" t="inlineStr"/>
       <c r="I28" s="17" t="inlineStr">
@@ -1868,6 +1865,7 @@
           <t>Per door — 2 signs per leaf</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
@@ -1894,9 +1892,8 @@
       <c r="F29" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="84">
-        <f>SUM(D29:F29)</f>
-        <v/>
+      <c r="G29" s="84" t="n">
+        <v>325</v>
       </c>
       <c r="H29" s="16" t="n"/>
       <c r="I29" s="21" t="inlineStr">
@@ -1935,9 +1932,8 @@
       <c r="F30" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="84">
-        <f>SUM(D30:F30)</f>
-        <v/>
+      <c r="G30" s="84" t="n">
+        <v>125</v>
       </c>
       <c r="H30" s="16" t="n"/>
       <c r="I30" s="17" t="inlineStr">
@@ -1976,9 +1972,8 @@
       <c r="F31" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="84">
-        <f>SUM(D31:F31)</f>
-        <v/>
+      <c r="G31" s="84" t="n">
+        <v>300</v>
       </c>
       <c r="H31" s="16" t="n"/>
       <c r="I31" s="21" t="inlineStr">
@@ -2017,9 +2012,8 @@
       <c r="F32" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="84">
-        <f>SUM(D32:F32)</f>
-        <v/>
+      <c r="G32" s="84" t="n">
+        <v>67.5</v>
       </c>
       <c r="H32" s="16" t="inlineStr"/>
       <c r="I32" s="25" t="inlineStr">
@@ -2027,6 +2021,7 @@
           <t>Covers ART 01 in EAS/FireDNA system. Common fault — appears on ~20% of doors surveyed.</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
@@ -2053,9 +2048,8 @@
       <c r="F33" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="84">
-        <f>SUM(D33:F33)</f>
-        <v/>
+      <c r="G33" s="84" t="n">
+        <v>500</v>
       </c>
       <c r="H33" s="16" t="n"/>
       <c r="I33" s="25" t="inlineStr">
@@ -2109,9 +2103,8 @@
       <c r="F35" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="84">
-        <f>SUM(D35:F35)</f>
-        <v/>
+      <c r="G35" s="84" t="n">
+        <v>170</v>
       </c>
       <c r="H35" s="16" t="n"/>
       <c r="I35" s="21" t="inlineStr">
@@ -2150,9 +2143,8 @@
       <c r="F36" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="84">
-        <f>SUM(D36:F36)</f>
-        <v/>
+      <c r="G36" s="84" t="n">
+        <v>300</v>
       </c>
       <c r="H36" s="16" t="n"/>
       <c r="I36" s="17" t="inlineStr">
@@ -2191,9 +2183,8 @@
       <c r="F37" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="84">
-        <f>SUM(D37:F37)</f>
-        <v/>
+      <c r="G37" s="84" t="n">
+        <v>40</v>
       </c>
       <c r="H37" s="16" t="n"/>
       <c r="I37" s="21" t="inlineStr">
@@ -2232,9 +2223,8 @@
       <c r="F38" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="84">
-        <f>SUM(D38:F38)</f>
-        <v/>
+      <c r="G38" s="84" t="n">
+        <v>200</v>
       </c>
       <c r="H38" s="16">
         <f>SUM(D38:G38)</f>
@@ -2271,9 +2261,8 @@
       <c r="F39" s="84" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="84">
-        <f>SUM(D39:F39)</f>
-        <v/>
+      <c r="G39" s="84" t="n">
+        <v>500</v>
       </c>
       <c r="H39" s="16" t="n"/>
       <c r="I39" s="21" t="inlineStr">
